--- a/AAII_Financials/Quarterly/HOTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HOTH_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -1088,7 +1088,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="E12" s="3">
         <v>700</v>

--- a/AAII_Financials/Quarterly/HOTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HOTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
   <si>
     <t>HOTH</t>
   </si>
@@ -656,123 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
@@ -782,8 +783,14 @@
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -871,8 +878,14 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -960,8 +973,14 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1049,8 +1068,14 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1082,85 +1107,87 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>900</v>
+      </c>
+      <c r="F12" s="3">
         <v>1200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>1500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>1000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>1000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>2000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>2200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>1800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>200</v>
-      </c>
-      <c r="P12" s="3">
-        <v>700</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>1300</v>
       </c>
       <c r="R12" s="3">
         <v>700</v>
       </c>
       <c r="S12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="T12" s="3">
+        <v>700</v>
+      </c>
+      <c r="U12" s="3">
         <v>1000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>100</v>
-      </c>
-      <c r="W12" s="3">
-        <v>200</v>
-      </c>
-      <c r="X12" s="3">
-        <v>400</v>
       </c>
       <c r="Y12" s="3">
         <v>200</v>
       </c>
       <c r="Z12" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA12" s="3">
         <v>200</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
+      <c r="AB12" s="3">
+        <v>200</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>3</v>
@@ -1171,8 +1198,14 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1260,8 +1293,14 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1349,8 +1388,14 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1438,8 +1483,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1468,8 +1519,10 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1480,74 +1533,74 @@
         <v>1700</v>
       </c>
       <c r="F17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="H17" s="3">
         <v>2200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3400</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I17" s="3">
-        <v>2300</v>
       </c>
       <c r="J17" s="3">
         <v>2700</v>
       </c>
       <c r="K17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="M17" s="3">
         <v>3400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>3900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>500</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1557,8 +1610,14 @@
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1569,74 +1628,74 @@
         <v>-1700</v>
       </c>
       <c r="F18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="H18" s="3">
         <v>-2200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-3400</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-2300</v>
       </c>
       <c r="J18" s="3">
         <v>-2700</v>
       </c>
       <c r="K18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="M18" s="3">
         <v>-3400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-3200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-4300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-2500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-3900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-500</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1646,8 +1705,14 @@
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1679,8 +1744,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1688,28 +1755,28 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>-100</v>
@@ -1718,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1753,11 +1820,11 @@
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0</v>
       </c>
       <c r="AC20" s="3" t="s">
         <v>3</v>
@@ -1768,8 +1835,14 @@
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1794,60 +1867,60 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>-3500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-3300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-3300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-4300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-2500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-1800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-3900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-1700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-1300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-500</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1857,8 +1930,14 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1916,20 +1995,20 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
@@ -1946,86 +2025,92 @@
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-2200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-3500</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-2700</v>
       </c>
       <c r="J23" s="3">
         <v>-2600</v>
       </c>
       <c r="K23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="L23" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="M23" s="3">
         <v>-3500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-3300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-3300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-4300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-3900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-1700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-1300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-500</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2035,8 +2120,14 @@
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2124,8 +2215,14 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2213,86 +2310,92 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-2200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-3500</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-2700</v>
       </c>
       <c r="J26" s="3">
         <v>-2600</v>
       </c>
       <c r="K26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="M26" s="3">
         <v>-3500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-3300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-3300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-4300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-3900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-1700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-500</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2302,86 +2405,92 @@
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-3500</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-2700</v>
       </c>
       <c r="J27" s="3">
         <v>-2600</v>
       </c>
       <c r="K27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="L27" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="M27" s="3">
         <v>-3500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-3300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-3300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-4300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-3900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-1700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-1300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-500</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2391,8 +2500,14 @@
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2480,8 +2595,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2569,8 +2690,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2658,8 +2785,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2747,8 +2880,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2756,28 +2895,28 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>100</v>
@@ -2786,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -2821,11 +2960,11 @@
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
       </c>
       <c r="AC32" s="3" t="s">
         <v>3</v>
@@ -2836,86 +2975,92 @@
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-3500</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-2700</v>
       </c>
       <c r="J33" s="3">
         <v>-2600</v>
       </c>
       <c r="K33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="L33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="M33" s="3">
         <v>-3500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-3300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-3300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-4300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-3900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-1700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-500</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,8 +3070,14 @@
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3014,86 +3165,92 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-3500</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-2700</v>
       </c>
       <c r="J35" s="3">
         <v>-2600</v>
       </c>
       <c r="K35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="L35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="M35" s="3">
         <v>-3500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-3300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-3300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-4300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-3900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-1700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-500</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3103,91 +3260,97 @@
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3197,8 +3360,14 @@
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3230,8 +3399,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3263,80 +3434,82 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F41" s="3">
         <v>11800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>11500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>13000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>6400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>8900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>11300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>6400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>8500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>12400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>15900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>19300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>4100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>4900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>4300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>1700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>3200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>4100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>5200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>700</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3352,68 +3525,74 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
+      <c r="D42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>1900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>1900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>2000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>1600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>2100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>1300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>2000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>800</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3426,11 +3605,11 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC42" s="3">
         <v>0</v>
@@ -3441,8 +3620,14 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3455,14 +3640,14 @@
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>100</v>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J43" s="3">
         <v>100</v>
@@ -3473,11 +3658,11 @@
       <c r="L43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
+      <c r="M43" s="3">
+        <v>100</v>
+      </c>
+      <c r="N43" s="3">
+        <v>100</v>
       </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
@@ -3491,11 +3676,11 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
@@ -3530,8 +3715,14 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3619,49 +3810,55 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="E45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
         <v>200</v>
       </c>
       <c r="G45" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H45" s="3">
         <v>200</v>
       </c>
       <c r="I45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J45" s="3">
         <v>200</v>
       </c>
       <c r="K45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="L45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M45" s="3">
         <v>100</v>
       </c>
       <c r="N45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O45" s="3">
         <v>100</v>
       </c>
       <c r="P45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q45" s="3">
         <v>100</v>
@@ -3682,16 +3879,16 @@
         <v>100</v>
       </c>
       <c r="W45" s="3">
+        <v>100</v>
+      </c>
+      <c r="X45" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y45" s="3">
         <v>200</v>
       </c>
-      <c r="X45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
+      <c r="Z45" s="3">
+        <v>0</v>
       </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
@@ -3708,80 +3905,86 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F46" s="3">
         <v>12100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>11900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>13400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>6700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>9500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>11900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>8500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>10600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>14800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>17600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>20500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>4800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>5500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>7000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>4900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>2600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>4100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>4200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>5300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>800</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3797,8 +4000,14 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3815,10 +4024,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3">
         <v>400</v>
@@ -3830,29 +4039,29 @@
         <v>400</v>
       </c>
       <c r="M47" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="N47" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="O47" s="3">
         <v>500</v>
       </c>
       <c r="P47" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>500</v>
+      </c>
+      <c r="R47" s="3">
         <v>400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>300</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,11 +4074,11 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -3886,8 +4095,14 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3895,22 +4110,22 @@
         <v>0</v>
       </c>
       <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -3954,11 +4169,11 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="3">
+        <v>0</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
@@ -3975,8 +4190,14 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4064,8 +4285,14 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4153,8 +4380,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4242,8 +4475,14 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4284,16 +4523,16 @@
         <v>0</v>
       </c>
       <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3">
-        <v>200</v>
-      </c>
-      <c r="S52" s="3">
-        <v>200</v>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T52" s="3">
         <v>200</v>
@@ -4304,11 +4543,11 @@
       <c r="V52" s="3">
         <v>200</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
+      <c r="W52" s="3">
+        <v>200</v>
+      </c>
+      <c r="X52" s="3">
+        <v>200</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
@@ -4316,11 +4555,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>0</v>
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC52" s="3">
         <v>0</v>
@@ -4331,8 +4570,14 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4420,80 +4665,86 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F54" s="3">
         <v>12100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>11900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>13500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>6800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>9900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>12300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>8900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>11000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>15200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>18000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>21000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>5200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>6000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>7400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>5300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>4300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>4400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>5500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>800</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4509,8 +4760,14 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4542,8 +4799,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4575,79 +4834,81 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>800</v>
-      </c>
-      <c r="G57" s="3">
-        <v>700</v>
-      </c>
-      <c r="H57" s="3">
-        <v>900</v>
       </c>
       <c r="I57" s="3">
         <v>700</v>
       </c>
       <c r="J57" s="3">
+        <v>900</v>
+      </c>
+      <c r="K57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
+        <v>700</v>
+      </c>
+      <c r="M57" s="3">
         <v>400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
         <v>200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>400</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3">
         <v>200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>100</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
+      <c r="Z57" s="3">
+        <v>0</v>
       </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
@@ -4664,8 +4925,14 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4753,59 +5020,65 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>600</v>
+      </c>
+      <c r="F59" s="3">
         <v>900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>700</v>
-      </c>
-      <c r="H59" s="3">
-        <v>100</v>
-      </c>
-      <c r="I59" s="3">
-        <v>100</v>
       </c>
       <c r="J59" s="3">
         <v>100</v>
       </c>
       <c r="K59" s="3">
+        <v>100</v>
+      </c>
+      <c r="L59" s="3">
+        <v>100</v>
+      </c>
+      <c r="M59" s="3">
         <v>500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>400</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
-      </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
       <c r="T59" s="3">
         <v>0</v>
       </c>
@@ -4816,22 +5089,22 @@
         <v>0</v>
       </c>
       <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="3">
         <v>200</v>
       </c>
-      <c r="X59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>0</v>
+      <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC59" s="3">
         <v>0</v>
@@ -4842,79 +5115,85 @@
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>700</v>
+      </c>
+      <c r="F60" s="3">
         <v>1600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>400</v>
       </c>
-      <c r="T60" s="3">
-        <v>0</v>
-      </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+      <c r="W60" s="3">
         <v>200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>300</v>
       </c>
-      <c r="X60" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
+      <c r="Z60" s="3">
+        <v>0</v>
       </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
@@ -4931,8 +5210,14 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5020,8 +5305,14 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5029,10 +5320,10 @@
         <v>0</v>
       </c>
       <c r="E62" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G62" s="3">
         <v>300</v>
@@ -5044,10 +5335,10 @@
         <v>300</v>
       </c>
       <c r="J62" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K62" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L62" s="3">
         <v>200</v>
@@ -5056,17 +5347,17 @@
         <v>200</v>
       </c>
       <c r="N62" s="3">
+        <v>200</v>
+      </c>
+      <c r="O62" s="3">
+        <v>200</v>
+      </c>
+      <c r="P62" s="3">
         <v>300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>300</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5079,11 +5370,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
-      </c>
-      <c r="W62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X62" s="3">
         <v>0</v>
@@ -5109,8 +5400,14 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5198,8 +5495,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5287,8 +5590,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5376,79 +5685,85 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="E66" s="3">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="F66" s="3">
         <v>1600</v>
       </c>
       <c r="G66" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H66" s="3">
         <v>1600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J66" s="3">
         <v>1300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1000</v>
-      </c>
-      <c r="O66" s="3">
-        <v>600</v>
-      </c>
-      <c r="P66" s="3">
-        <v>600</v>
       </c>
       <c r="Q66" s="3">
         <v>600</v>
       </c>
       <c r="R66" s="3">
+        <v>600</v>
+      </c>
+      <c r="S66" s="3">
+        <v>600</v>
+      </c>
+      <c r="T66" s="3">
         <v>500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>400</v>
       </c>
-      <c r="T66" s="3">
-        <v>0</v>
-      </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
+        <v>0</v>
+      </c>
+      <c r="W66" s="3">
         <v>200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>300</v>
       </c>
-      <c r="X66" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
+      <c r="Z66" s="3">
+        <v>0</v>
       </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
@@ -5465,8 +5780,14 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5498,8 +5819,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5587,8 +5910,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5676,8 +6005,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5765,8 +6100,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5854,80 +6195,86 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-52900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-51200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-49200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-47300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-45100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-41600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-39000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-36300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-33700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-30200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-27000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-23700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-19400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-18700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-16500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-14000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-12200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-8300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-6600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-5300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-4500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5943,8 +6290,14 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6032,8 +6385,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6121,8 +6480,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6210,80 +6575,86 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F76" s="3">
         <v>10500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>10000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>11900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>11200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>7900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>9900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>13300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>16600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>19900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>4600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>5400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>6800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>4800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>2400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>4300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>4200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>5400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>700</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6299,8 +6670,14 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6388,91 +6765,97 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6482,86 +6865,92 @@
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-3500</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-2700</v>
       </c>
       <c r="J81" s="3">
         <v>-2600</v>
       </c>
       <c r="K81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="L81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="M81" s="3">
         <v>-3500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-3300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-3300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-4300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-3900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-1700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-500</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6571,8 +6960,14 @@
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6604,8 +6999,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6678,11 +7075,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3">
+        <v>0</v>
       </c>
       <c r="AC83" s="3" t="s">
         <v>3</v>
@@ -6693,8 +7090,14 @@
       <c r="AE83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6782,8 +7185,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6871,8 +7280,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6960,8 +7375,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7049,8 +7470,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7138,86 +7565,92 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-2200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-3900</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-2800</v>
       </c>
       <c r="N89" s="3">
         <v>-2700</v>
       </c>
       <c r="O89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="P89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-2400</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-1500</v>
       </c>
       <c r="T89" s="3">
         <v>-1600</v>
       </c>
       <c r="U89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="V89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="W89" s="3">
         <v>-1000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-400</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7227,8 +7660,14 @@
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7260,8 +7699,10 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7281,23 +7722,23 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -7349,8 +7790,14 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7438,8 +7885,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7527,13 +7980,19 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -7548,47 +8007,47 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>1200</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>1000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-1700</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-900</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
@@ -7601,11 +8060,11 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
       </c>
       <c r="AC94" s="3" t="s">
         <v>3</v>
@@ -7616,8 +8075,14 @@
       <c r="AE94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7649,8 +8114,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7738,8 +8205,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7827,8 +8300,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7916,8 +8395,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8005,86 +8490,92 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>2400</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>8900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>6000</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>18400</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>4500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>4200</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>1600</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>5900</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>1200</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8094,20 +8585,26 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
@@ -8138,11 +8635,11 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
@@ -8156,11 +8653,11 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -8183,86 +8680,92 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>6600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-2400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>4900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-2200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-3900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-3500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>16700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>2700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-1100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>5100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>800</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8270,6 +8773,12 @@
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HOTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HOTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="92">
   <si>
     <t>HOTH</t>
   </si>
@@ -656,127 +656,128 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
@@ -789,8 +790,11 @@
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -884,8 +888,11 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -979,8 +986,11 @@
       <c r="AG9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1074,8 +1084,11 @@
       <c r="AG10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1109,88 +1122,89 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>600</v>
+      </c>
+      <c r="E12" s="3">
         <v>500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>900</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1500</v>
       </c>
       <c r="J12" s="3">
         <v>1500</v>
       </c>
       <c r="K12" s="3">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="L12" s="3">
         <v>1000</v>
       </c>
       <c r="M12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N12" s="3">
         <v>2000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>200</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>400</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>200</v>
       </c>
       <c r="AB12" s="3">
         <v>200</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
+      <c r="AC12" s="3">
+        <v>200</v>
       </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
@@ -1204,8 +1218,11 @@
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1299,8 +1316,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1394,8 +1414,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1489,8 +1512,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1521,89 +1547,90 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E17" s="3">
         <v>2100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>800</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>600</v>
       </c>
       <c r="Z17" s="3">
         <v>600</v>
       </c>
       <c r="AA17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB17" s="3">
         <v>800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>500</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1616,8 +1643,11 @@
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1625,80 +1655,80 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-800</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-600</v>
       </c>
       <c r="Z18" s="3">
         <v>-600</v>
       </c>
       <c r="AA18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-500</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1711,8 +1741,11 @@
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1746,8 +1779,9 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1761,35 +1795,35 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1826,8 +1860,8 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
+      <c r="AC20" s="3">
+        <v>0</v>
       </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
@@ -1841,8 +1875,11 @@
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1873,57 +1910,57 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>-3500</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-3300</v>
       </c>
       <c r="O21" s="3">
         <v>-3300</v>
       </c>
       <c r="P21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-800</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-600</v>
       </c>
       <c r="Z21" s="3">
         <v>-600</v>
       </c>
       <c r="AA21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-500</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1936,8 +1973,11 @@
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2001,17 +2041,17 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
+      <c r="AA22" s="3">
+        <v>0</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
@@ -2031,89 +2071,92 @@
       <c r="AG22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3500</v>
-      </c>
-      <c r="N23" s="3">
-        <v>-3300</v>
       </c>
       <c r="O23" s="3">
         <v>-3300</v>
       </c>
       <c r="P23" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-800</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-600</v>
       </c>
       <c r="Z23" s="3">
         <v>-600</v>
       </c>
       <c r="AA23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-500</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2126,8 +2169,11 @@
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2221,8 +2267,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2316,89 +2365,92 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3500</v>
-      </c>
-      <c r="N26" s="3">
-        <v>-3300</v>
       </c>
       <c r="O26" s="3">
         <v>-3300</v>
       </c>
       <c r="P26" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-800</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-600</v>
       </c>
       <c r="Z26" s="3">
         <v>-600</v>
       </c>
       <c r="AA26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-500</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2411,89 +2463,92 @@
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3500</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-3300</v>
       </c>
       <c r="O27" s="3">
         <v>-3300</v>
       </c>
       <c r="P27" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-800</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-600</v>
       </c>
       <c r="Z27" s="3">
         <v>-600</v>
       </c>
       <c r="AA27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-500</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2506,8 +2561,11 @@
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2601,8 +2659,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2696,8 +2757,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2791,8 +2855,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2886,8 +2953,11 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2901,35 +2971,35 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2966,8 +3036,8 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
+      <c r="AC32" s="3">
+        <v>0</v>
       </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
@@ -2981,89 +3051,92 @@
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3500</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-3300</v>
       </c>
       <c r="O33" s="3">
         <v>-3300</v>
       </c>
       <c r="P33" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-800</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-600</v>
       </c>
       <c r="Z33" s="3">
         <v>-600</v>
       </c>
       <c r="AA33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-500</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3076,8 +3149,11 @@
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3171,89 +3247,92 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3500</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-3300</v>
       </c>
       <c r="O35" s="3">
         <v>-3300</v>
       </c>
       <c r="P35" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-800</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-600</v>
       </c>
       <c r="Z35" s="3">
         <v>-600</v>
       </c>
       <c r="AA35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-500</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3266,94 +3345,97 @@
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3366,8 +3448,11 @@
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3401,8 +3486,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3436,83 +3522,84 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E41" s="3">
         <v>7600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>13000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>15900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>700</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3531,16 +3618,19 @@
       <c r="AG41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
+      <c r="E42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -3549,52 +3639,52 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
         <v>200</v>
       </c>
       <c r="J42" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K42" s="3">
         <v>300</v>
       </c>
       <c r="L42" s="3">
-        <v>1900</v>
+        <v>300</v>
       </c>
       <c r="M42" s="3">
         <v>1900</v>
       </c>
       <c r="N42" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O42" s="3">
         <v>2000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>500</v>
-      </c>
-      <c r="U42" s="3">
-        <v>800</v>
       </c>
       <c r="V42" s="3">
         <v>800</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>3</v>
+      <c r="W42" s="3">
+        <v>800</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>3</v>
@@ -3611,8 +3701,8 @@
       <c r="AB42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
@@ -3626,8 +3716,11 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3646,11 +3739,11 @@
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K43" s="3">
         <v>100</v>
@@ -3664,8 +3757,8 @@
       <c r="N43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
+      <c r="O43" s="3">
+        <v>100</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
@@ -3682,8 +3775,8 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -3721,8 +3814,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3816,31 +3912,34 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
         <v>800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>200</v>
       </c>
       <c r="K45" s="3">
         <v>200</v>
@@ -3849,19 +3948,19 @@
         <v>200</v>
       </c>
       <c r="M45" s="3">
+        <v>200</v>
+      </c>
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>100</v>
       </c>
       <c r="R45" s="3">
         <v>100</v>
@@ -3885,13 +3984,13 @@
         <v>100</v>
       </c>
       <c r="Y45" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
-      <c r="Z45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
+      <c r="AA45" s="3">
+        <v>0</v>
       </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
@@ -3911,83 +4010,86 @@
       <c r="AG45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E46" s="3">
         <v>8400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>17600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>20500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>7000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>800</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4006,8 +4108,11 @@
       <c r="AG46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4030,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K47" s="3">
         <v>400</v>
@@ -4045,7 +4150,7 @@
         <v>400</v>
       </c>
       <c r="O47" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="P47" s="3">
         <v>500</v>
@@ -4054,17 +4159,17 @@
         <v>500</v>
       </c>
       <c r="R47" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="S47" s="3">
         <v>400</v>
       </c>
       <c r="T47" s="3">
+        <v>400</v>
+      </c>
+      <c r="U47" s="3">
         <v>300</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4080,8 +4185,8 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
@@ -4101,8 +4206,11 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4110,11 +4218,11 @@
         <v>0</v>
       </c>
       <c r="E48" s="3">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3">
         <v>100</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4127,8 +4235,8 @@
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -4175,8 +4283,8 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
+      <c r="AA48" s="3">
+        <v>0</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
@@ -4196,8 +4304,11 @@
       <c r="AG48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4291,8 +4402,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4386,8 +4500,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4481,8 +4598,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4529,13 +4649,13 @@
         <v>0</v>
       </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T52" s="3">
-        <v>200</v>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U52" s="3">
         <v>200</v>
@@ -4549,8 +4669,8 @@
       <c r="X52" s="3">
         <v>200</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
+      <c r="Y52" s="3">
+        <v>200</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
@@ -4561,8 +4681,8 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC52" s="3">
-        <v>0</v>
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD52" s="3">
         <v>0</v>
@@ -4576,8 +4696,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4671,83 +4794,86 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E54" s="3">
         <v>8500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>12100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>18000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>7400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>800</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4766,8 +4892,11 @@
       <c r="AG54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4801,8 +4930,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4836,82 +4966,83 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>300</v>
+      </c>
+      <c r="E57" s="3">
         <v>400</v>
       </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
       <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>900</v>
-      </c>
-      <c r="K57" s="3">
-        <v>700</v>
       </c>
       <c r="L57" s="3">
         <v>700</v>
       </c>
       <c r="M57" s="3">
+        <v>700</v>
+      </c>
+      <c r="N57" s="3">
         <v>400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
       <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
         <v>200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>400</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
       <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3">
         <v>200</v>
-      </c>
-      <c r="X57" s="3">
-        <v>100</v>
       </c>
       <c r="Y57" s="3">
         <v>100</v>
       </c>
       <c r="Z57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>0</v>
       </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
@@ -4931,8 +5062,11 @@
       <c r="AG57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5026,8 +5160,11 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5035,22 +5172,22 @@
         <v>300</v>
       </c>
       <c r="E59" s="3">
+        <v>300</v>
+      </c>
+      <c r="F59" s="3">
         <v>600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>700</v>
-      </c>
-      <c r="J59" s="3">
-        <v>100</v>
       </c>
       <c r="K59" s="3">
         <v>100</v>
@@ -5059,29 +5196,29 @@
         <v>100</v>
       </c>
       <c r="M59" s="3">
+        <v>100</v>
+      </c>
+      <c r="N59" s="3">
         <v>500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>400</v>
-      </c>
-      <c r="P59" s="3">
-        <v>200</v>
       </c>
       <c r="Q59" s="3">
         <v>200</v>
       </c>
       <c r="R59" s="3">
+        <v>200</v>
+      </c>
+      <c r="S59" s="3">
         <v>500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>400</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
-      </c>
       <c r="U59" s="3">
         <v>0</v>
       </c>
@@ -5095,19 +5232,19 @@
         <v>0</v>
       </c>
       <c r="Y59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="3">
         <v>200</v>
       </c>
-      <c r="Z59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
+      <c r="AA59" s="3">
+        <v>0</v>
       </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD59" s="3">
         <v>0</v>
@@ -5121,82 +5258,85 @@
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>700</v>
+      </c>
+      <c r="E60" s="3">
         <v>600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1000</v>
-      </c>
-      <c r="K60" s="3">
-        <v>800</v>
       </c>
       <c r="L60" s="3">
         <v>800</v>
       </c>
       <c r="M60" s="3">
+        <v>800</v>
+      </c>
+      <c r="N60" s="3">
         <v>900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>300</v>
-      </c>
-      <c r="R60" s="3">
-        <v>600</v>
       </c>
       <c r="S60" s="3">
         <v>600</v>
       </c>
       <c r="T60" s="3">
+        <v>600</v>
+      </c>
+      <c r="U60" s="3">
         <v>500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>400</v>
       </c>
-      <c r="V60" s="3">
-        <v>0</v>
-      </c>
       <c r="W60" s="3">
+        <v>0</v>
+      </c>
+      <c r="X60" s="3">
         <v>200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>300</v>
       </c>
-      <c r="Z60" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
+      <c r="AA60" s="3">
+        <v>0</v>
       </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
@@ -5216,8 +5356,11 @@
       <c r="AG60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5311,8 +5454,11 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5326,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="G62" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
         <v>300</v>
@@ -5341,7 +5487,7 @@
         <v>300</v>
       </c>
       <c r="L62" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M62" s="3">
         <v>200</v>
@@ -5353,13 +5499,13 @@
         <v>200</v>
       </c>
       <c r="P62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q62" s="3">
         <v>300</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
+      <c r="R62" s="3">
+        <v>300</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
@@ -5376,8 +5522,8 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="X62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y62" s="3">
         <v>0</v>
@@ -5406,8 +5552,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5501,8 +5650,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5596,8 +5748,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5691,8 +5846,11 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -5703,40 +5861,40 @@
         <v>700</v>
       </c>
       <c r="F66" s="3">
+        <v>700</v>
+      </c>
+      <c r="G66" s="3">
         <v>1600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2000</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1600</v>
       </c>
       <c r="I66" s="3">
         <v>1600</v>
       </c>
       <c r="J66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K66" s="3">
         <v>1300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1000</v>
-      </c>
-      <c r="L66" s="3">
-        <v>1100</v>
       </c>
       <c r="M66" s="3">
         <v>1100</v>
       </c>
       <c r="N66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O66" s="3">
         <v>1800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>600</v>
       </c>
       <c r="R66" s="3">
         <v>600</v>
@@ -5745,28 +5903,28 @@
         <v>600</v>
       </c>
       <c r="T66" s="3">
+        <v>600</v>
+      </c>
+      <c r="U66" s="3">
         <v>500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>400</v>
       </c>
-      <c r="V66" s="3">
-        <v>0</v>
-      </c>
       <c r="W66" s="3">
+        <v>0</v>
+      </c>
+      <c r="X66" s="3">
         <v>200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>300</v>
       </c>
-      <c r="Z66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
+      <c r="AA66" s="3">
+        <v>0</v>
       </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
@@ -5786,8 +5944,11 @@
       <c r="AG66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5821,8 +5982,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5916,8 +6078,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6011,8 +6176,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6106,8 +6274,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6201,83 +6372,86 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-56600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-55000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-52900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-51200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-49200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-47300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-45100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-41600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-39000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-36300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-33700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-30200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-27000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-23700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-19400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-18700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-16500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-14000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-12200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-8300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-6600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-4500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6296,8 +6470,11 @@
       <c r="AG72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6391,8 +6568,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6486,8 +6666,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6581,83 +6764,86 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E76" s="3">
         <v>7800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>19900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>700</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6676,8 +6862,11 @@
       <c r="AG76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6771,94 +6960,97 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6871,89 +7063,92 @@
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3500</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-3300</v>
       </c>
       <c r="O81" s="3">
         <v>-3300</v>
       </c>
       <c r="P81" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-800</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-600</v>
       </c>
       <c r="Z81" s="3">
         <v>-600</v>
       </c>
       <c r="AA81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-500</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6966,8 +7161,11 @@
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7001,8 +7199,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7081,8 +7280,8 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
+      <c r="AC83" s="3">
+        <v>0</v>
       </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
@@ -7096,8 +7295,11 @@
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7191,8 +7393,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7286,8 +7491,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7381,8 +7589,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7476,8 +7687,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7571,89 +7785,92 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-400</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7666,8 +7883,11 @@
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7701,8 +7921,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7731,17 +7952,17 @@
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
@@ -7796,8 +8017,11 @@
       <c r="AG91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7891,8 +8115,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7986,16 +8213,19 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -8013,44 +8243,44 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>1200</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1700</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-900</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
@@ -8066,8 +8296,8 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
+      <c r="AC94" s="3">
+        <v>0</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
@@ -8081,8 +8311,11 @@
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8116,8 +8349,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8211,8 +8445,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8306,8 +8543,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8401,8 +8641,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8496,77 +8739,80 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>2400</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>8900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>6000</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
       <c r="N100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O100" s="3">
         <v>-100</v>
       </c>
       <c r="P100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q100" s="3">
         <v>18400</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>4500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4200</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>1600</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>5900</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
@@ -8574,11 +8820,11 @@
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>1200</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8591,8 +8837,11 @@
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8600,14 +8849,14 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
@@ -8641,8 +8890,8 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
+      <c r="S101" s="3">
+        <v>0</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
@@ -8659,8 +8908,8 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -8686,89 +8935,92 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-3900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>16700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>800</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8779,6 +9031,9 @@
         <v>3</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HOTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HOTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="92">
   <si>
     <t>HOTH</t>
   </si>
@@ -656,131 +656,132 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
@@ -793,31 +794,34 @@
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -891,8 +895,11 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -989,8 +996,11 @@
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1087,8 +1097,11 @@
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1123,91 +1136,92 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>900</v>
+      </c>
+      <c r="E12" s="3">
         <v>600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>900</v>
       </c>
-      <c r="G12" s="3">
-        <v>1200</v>
-      </c>
       <c r="H12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I12" s="3">
         <v>700</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>900</v>
-      </c>
-      <c r="J12" s="3">
-        <v>1500</v>
       </c>
       <c r="K12" s="3">
         <v>1500</v>
       </c>
       <c r="L12" s="3">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="M12" s="3">
         <v>1000</v>
       </c>
       <c r="N12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O12" s="3">
         <v>2000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>1000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>400</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>200</v>
       </c>
       <c r="AC12" s="3">
         <v>200</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
+      <c r="AD12" s="3">
+        <v>200</v>
       </c>
       <c r="AE12" s="3" t="s">
         <v>3</v>
@@ -1221,8 +1235,11 @@
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1319,16 +1336,19 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1336,11 +1356,11 @@
       <c r="G14" s="3">
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1417,8 +1437,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1515,8 +1538,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1548,92 +1574,93 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E17" s="3">
         <v>1600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>800</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>600</v>
       </c>
       <c r="AA17" s="3">
         <v>600</v>
       </c>
       <c r="AB17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC17" s="3">
         <v>800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>500</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1646,92 +1673,95 @@
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-2100</v>
       </c>
       <c r="E18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-3400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-4300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-3900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-800</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-600</v>
       </c>
       <c r="AA18" s="3">
         <v>-600</v>
       </c>
       <c r="AB18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-500</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1744,8 +1774,11 @@
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1780,53 +1813,54 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1863,8 +1897,8 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
+      <c r="AD20" s="3">
+        <v>0</v>
       </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
@@ -1878,31 +1912,34 @@
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-2200</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1913,57 +1950,57 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>-3500</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-3300</v>
       </c>
       <c r="P21" s="3">
         <v>-3300</v>
       </c>
       <c r="Q21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="R21" s="3">
         <v>-4300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-800</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>-600</v>
       </c>
       <c r="AA21" s="3">
         <v>-600</v>
       </c>
       <c r="AB21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-500</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1976,31 +2013,34 @@
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2044,17 +2084,17 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
+      <c r="AB22" s="3">
+        <v>0</v>
       </c>
       <c r="AC22" s="3" t="s">
         <v>3</v>
@@ -2074,92 +2114,95 @@
       <c r="AH22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3500</v>
-      </c>
-      <c r="O23" s="3">
-        <v>-3300</v>
       </c>
       <c r="P23" s="3">
         <v>-3300</v>
       </c>
       <c r="Q23" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="R23" s="3">
         <v>-4300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-800</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-600</v>
       </c>
       <c r="AA23" s="3">
         <v>-600</v>
       </c>
       <c r="AB23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-500</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2172,31 +2215,34 @@
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -2270,8 +2316,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2368,92 +2417,95 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3500</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-3300</v>
       </c>
       <c r="P26" s="3">
         <v>-3300</v>
       </c>
       <c r="Q26" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="R26" s="3">
         <v>-4300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-800</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-600</v>
       </c>
       <c r="AA26" s="3">
         <v>-600</v>
       </c>
       <c r="AB26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-500</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2466,92 +2518,95 @@
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3500</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-3300</v>
       </c>
       <c r="P27" s="3">
         <v>-3300</v>
       </c>
       <c r="Q27" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="R27" s="3">
         <v>-4300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-800</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-600</v>
       </c>
       <c r="AA27" s="3">
         <v>-600</v>
       </c>
       <c r="AB27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-500</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2564,8 +2619,11 @@
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2662,8 +2720,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2760,8 +2821,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2858,8 +2922,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2956,53 +3023,56 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3039,8 +3109,8 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
+      <c r="AD32" s="3">
+        <v>0</v>
       </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
@@ -3054,92 +3124,95 @@
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3500</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-3300</v>
       </c>
       <c r="P33" s="3">
         <v>-3300</v>
       </c>
       <c r="Q33" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="R33" s="3">
         <v>-4300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-800</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-600</v>
       </c>
       <c r="AA33" s="3">
         <v>-600</v>
       </c>
       <c r="AB33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-500</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3152,8 +3225,11 @@
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3250,92 +3326,95 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3500</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-3300</v>
       </c>
       <c r="P35" s="3">
         <v>-3300</v>
       </c>
       <c r="Q35" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="R35" s="3">
         <v>-4300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-800</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-600</v>
       </c>
       <c r="AA35" s="3">
         <v>-600</v>
       </c>
       <c r="AB35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-500</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3348,97 +3427,100 @@
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3451,8 +3533,11 @@
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3487,8 +3572,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3523,86 +3609,87 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E41" s="3">
         <v>9700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>13000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>15900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>19300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>700</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,16 +3708,19 @@
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -3642,52 +3732,52 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
         <v>200</v>
       </c>
       <c r="K42" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L42" s="3">
         <v>300</v>
       </c>
       <c r="M42" s="3">
-        <v>1900</v>
+        <v>300</v>
       </c>
       <c r="N42" s="3">
         <v>1900</v>
       </c>
       <c r="O42" s="3">
+        <v>1900</v>
+      </c>
+      <c r="P42" s="3">
         <v>2000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>500</v>
-      </c>
-      <c r="V42" s="3">
-        <v>800</v>
       </c>
       <c r="W42" s="3">
         <v>800</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>3</v>
+      <c r="X42" s="3">
+        <v>800</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>3</v>
@@ -3704,8 +3794,8 @@
       <c r="AC42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
+      <c r="AD42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE42" s="3">
         <v>0</v>
@@ -3719,8 +3809,11 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3742,11 +3835,11 @@
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L43" s="3">
         <v>100</v>
@@ -3760,8 +3853,8 @@
       <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
+      <c r="P43" s="3">
+        <v>100</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
@@ -3778,8 +3871,8 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -3817,31 +3910,34 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3915,34 +4011,37 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>800</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F45" s="3">
+        <v>600</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>100</v>
-      </c>
-      <c r="K45" s="3">
-        <v>200</v>
       </c>
       <c r="L45" s="3">
         <v>200</v>
@@ -3951,19 +4050,19 @@
         <v>200</v>
       </c>
       <c r="N45" s="3">
+        <v>200</v>
+      </c>
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
-      </c>
-      <c r="R45" s="3">
-        <v>100</v>
       </c>
       <c r="S45" s="3">
         <v>100</v>
@@ -3987,13 +4086,13 @@
         <v>100</v>
       </c>
       <c r="Z45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA45" s="3">
         <v>200</v>
       </c>
-      <c r="AA45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>3</v>
+      <c r="AB45" s="3">
+        <v>0</v>
       </c>
       <c r="AC45" s="3" t="s">
         <v>3</v>
@@ -4013,86 +4112,89 @@
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E46" s="3">
         <v>10000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>17600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>20500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>7000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>800</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4111,8 +4213,11 @@
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4138,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="K47" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="L47" s="3">
         <v>400</v>
@@ -4153,7 +4258,7 @@
         <v>400</v>
       </c>
       <c r="P47" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Q47" s="3">
         <v>500</v>
@@ -4162,17 +4267,17 @@
         <v>500</v>
       </c>
       <c r="S47" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="T47" s="3">
         <v>400</v>
       </c>
       <c r="U47" s="3">
+        <v>400</v>
+      </c>
+      <c r="V47" s="3">
         <v>300</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4188,8 +4293,8 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC47" s="3">
         <v>0</v>
@@ -4209,8 +4314,11 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4221,11 +4329,11 @@
         <v>0</v>
       </c>
       <c r="F48" s="3">
+        <v>0</v>
+      </c>
+      <c r="G48" s="3">
         <v>100</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4238,8 +4346,8 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -4286,8 +4394,8 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>3</v>
+      <c r="AB48" s="3">
+        <v>0</v>
       </c>
       <c r="AC48" s="3" t="s">
         <v>3</v>
@@ -4307,8 +4415,11 @@
       <c r="AH48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4405,8 +4516,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4503,8 +4617,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4601,31 +4718,34 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4652,13 +4772,13 @@
         <v>0</v>
       </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>100</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U52" s="3">
-        <v>200</v>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V52" s="3">
         <v>200</v>
@@ -4672,8 +4792,8 @@
       <c r="Y52" s="3">
         <v>200</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
+      <c r="Z52" s="3">
+        <v>200</v>
       </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
@@ -4684,8 +4804,8 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD52" s="3">
-        <v>0</v>
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE52" s="3">
         <v>0</v>
@@ -4699,8 +4819,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4797,86 +4920,89 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E54" s="3">
         <v>10000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>12100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>18000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>7400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>800</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4895,8 +5021,11 @@
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4931,8 +5060,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4967,85 +5097,86 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
         <v>300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
       <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>900</v>
-      </c>
-      <c r="L57" s="3">
-        <v>700</v>
       </c>
       <c r="M57" s="3">
         <v>700</v>
       </c>
       <c r="N57" s="3">
+        <v>700</v>
+      </c>
+      <c r="O57" s="3">
         <v>400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>100</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
       <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
         <v>200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>400</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
-      </c>
       <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3">
         <v>200</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>100</v>
       </c>
       <c r="Z57" s="3">
         <v>100</v>
       </c>
       <c r="AA57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="AB57" s="3">
+        <v>0</v>
       </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
@@ -5065,8 +5196,11 @@
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5163,34 +5297,37 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>300</v>
-      </c>
-      <c r="E59" s="3">
-        <v>300</v>
-      </c>
-      <c r="F59" s="3">
-        <v>600</v>
-      </c>
-      <c r="G59" s="3">
-        <v>900</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I59" s="3">
-        <v>600</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>700</v>
-      </c>
-      <c r="K59" s="3">
-        <v>100</v>
       </c>
       <c r="L59" s="3">
         <v>100</v>
@@ -5199,29 +5336,29 @@
         <v>100</v>
       </c>
       <c r="N59" s="3">
+        <v>100</v>
+      </c>
+      <c r="O59" s="3">
         <v>500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>400</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>200</v>
       </c>
       <c r="R59" s="3">
         <v>200</v>
       </c>
       <c r="S59" s="3">
+        <v>200</v>
+      </c>
+      <c r="T59" s="3">
         <v>500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>400</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
-      </c>
       <c r="V59" s="3">
         <v>0</v>
       </c>
@@ -5235,19 +5372,19 @@
         <v>0</v>
       </c>
       <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3">
         <v>200</v>
       </c>
-      <c r="AA59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB59" s="3" t="s">
-        <v>3</v>
+      <c r="AB59" s="3">
+        <v>0</v>
       </c>
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD59" s="3">
-        <v>0</v>
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE59" s="3">
         <v>0</v>
@@ -5261,85 +5398,88 @@
       <c r="AH59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>800</v>
+      </c>
+      <c r="E60" s="3">
         <v>700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1000</v>
-      </c>
-      <c r="L60" s="3">
-        <v>800</v>
       </c>
       <c r="M60" s="3">
         <v>800</v>
       </c>
       <c r="N60" s="3">
+        <v>800</v>
+      </c>
+      <c r="O60" s="3">
         <v>900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>300</v>
-      </c>
-      <c r="S60" s="3">
-        <v>600</v>
       </c>
       <c r="T60" s="3">
         <v>600</v>
       </c>
       <c r="U60" s="3">
+        <v>600</v>
+      </c>
+      <c r="V60" s="3">
         <v>500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>400</v>
       </c>
-      <c r="W60" s="3">
-        <v>0</v>
-      </c>
       <c r="X60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="3">
         <v>200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>300</v>
       </c>
-      <c r="AA60" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
+      <c r="AB60" s="3">
+        <v>0</v>
       </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
@@ -5359,8 +5499,11 @@
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5457,25 +5600,28 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>300</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I62" s="3">
         <v>300</v>
@@ -5490,7 +5636,7 @@
         <v>300</v>
       </c>
       <c r="M62" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N62" s="3">
         <v>200</v>
@@ -5502,13 +5648,13 @@
         <v>200</v>
       </c>
       <c r="Q62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R62" s="3">
         <v>300</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
+      <c r="S62" s="3">
+        <v>300</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
@@ -5525,8 +5671,8 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
@@ -5555,8 +5701,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5653,8 +5802,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5751,8 +5903,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5849,13 +6004,16 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E66" s="3">
         <v>700</v>
@@ -5864,40 +6022,40 @@
         <v>700</v>
       </c>
       <c r="G66" s="3">
+        <v>700</v>
+      </c>
+      <c r="H66" s="3">
         <v>1600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1600</v>
       </c>
       <c r="J66" s="3">
         <v>1600</v>
       </c>
       <c r="K66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L66" s="3">
         <v>1300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1000</v>
-      </c>
-      <c r="M66" s="3">
-        <v>1100</v>
       </c>
       <c r="N66" s="3">
         <v>1100</v>
       </c>
       <c r="O66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P66" s="3">
         <v>1800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1000</v>
-      </c>
-      <c r="R66" s="3">
-        <v>600</v>
       </c>
       <c r="S66" s="3">
         <v>600</v>
@@ -5906,28 +6064,28 @@
         <v>600</v>
       </c>
       <c r="U66" s="3">
+        <v>600</v>
+      </c>
+      <c r="V66" s="3">
         <v>500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>400</v>
       </c>
-      <c r="W66" s="3">
-        <v>0</v>
-      </c>
       <c r="X66" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="3">
         <v>200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>300</v>
       </c>
-      <c r="AA66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
+      <c r="AB66" s="3">
+        <v>0</v>
       </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
@@ -5947,8 +6105,11 @@
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5983,8 +6144,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6081,8 +6243,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6179,8 +6344,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6277,8 +6445,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6375,86 +6546,89 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-58700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-56600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-55000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-52900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-51200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-49200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-47300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-45100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-41600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-39000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-36300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-33700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-30200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-27000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-23700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-19400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-18700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-16500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-14000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-12200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-8300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-6600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6473,8 +6647,11 @@
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6571,8 +6748,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6669,8 +6849,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6767,86 +6950,89 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E76" s="3">
         <v>9300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>19900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>700</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6865,8 +7051,11 @@
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6963,97 +7152,100 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
@@ -7066,92 +7258,95 @@
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3500</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-3300</v>
       </c>
       <c r="P81" s="3">
         <v>-3300</v>
       </c>
       <c r="Q81" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="R81" s="3">
         <v>-4300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-800</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-600</v>
       </c>
       <c r="AA81" s="3">
         <v>-600</v>
       </c>
       <c r="AB81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-500</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
@@ -7164,8 +7359,11 @@
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7200,31 +7398,32 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7283,8 +7482,8 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
+      <c r="AD83" s="3">
+        <v>0</v>
       </c>
       <c r="AE83" s="3" t="s">
         <v>3</v>
@@ -7298,8 +7497,11 @@
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7396,8 +7598,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7494,8 +7699,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7592,8 +7800,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7690,8 +7901,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7788,8 +8002,11 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7797,83 +8014,83 @@
         <v>-1600</v>
       </c>
       <c r="E89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-400</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7886,8 +8103,11 @@
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7922,31 +8142,32 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-100</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
@@ -7955,17 +8176,17 @@
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -8020,8 +8241,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8118,8 +8342,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8216,8 +8443,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8227,63 +8457,63 @@
       <c r="E94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>1200</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1700</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-900</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
@@ -8299,8 +8529,8 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
+      <c r="AD94" s="3">
+        <v>0</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>3</v>
@@ -8314,8 +8544,11 @@
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8350,31 +8583,32 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8448,8 +8682,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8546,8 +8783,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8644,8 +8884,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8742,80 +8985,83 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>3700</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>2400</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>8900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>6000</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
         <v>0</v>
       </c>
       <c r="O100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P100" s="3">
         <v>-100</v>
       </c>
       <c r="Q100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R100" s="3">
         <v>18400</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>4500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4200</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>1600</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>5900</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -8823,11 +9069,11 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>1200</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8840,22 +9086,25 @@
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G101" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
@@ -8893,8 +9142,8 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
+      <c r="T101" s="3">
+        <v>0</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
@@ -8911,8 +9160,8 @@
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA101" s="3">
         <v>0</v>
@@ -8938,92 +9187,95 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E102" s="3">
         <v>2100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>16700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>800</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
@@ -9034,6 +9286,9 @@
         <v>3</v>
       </c>
       <c r="AH102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HOTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HOTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="92">
   <si>
     <t>HOTH</t>
   </si>
@@ -656,138 +656,139 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
@@ -797,8 +798,14 @@
       <c r="AI7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -823,11 +830,11 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -898,8 +905,14 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -999,8 +1012,14 @@
       <c r="AI9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1100,8 +1119,14 @@
       <c r="AI10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1137,97 +1162,99 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F12" s="3">
         <v>900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K12" s="3">
+        <v>700</v>
+      </c>
+      <c r="L12" s="3">
         <v>900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="M12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O12" s="3">
         <v>1000</v>
       </c>
-      <c r="I12" s="3">
-        <v>700</v>
-      </c>
-      <c r="J12" s="3">
-        <v>900</v>
-      </c>
-      <c r="K12" s="3">
-        <v>1500</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1500</v>
-      </c>
-      <c r="M12" s="3">
+      <c r="P12" s="3">
         <v>1000</v>
       </c>
-      <c r="N12" s="3">
-        <v>1000</v>
-      </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>2000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>2200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>1800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>1600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>200</v>
-      </c>
-      <c r="T12" s="3">
-        <v>700</v>
-      </c>
-      <c r="U12" s="3">
-        <v>1300</v>
       </c>
       <c r="V12" s="3">
         <v>700</v>
       </c>
       <c r="W12" s="3">
+        <v>1300</v>
+      </c>
+      <c r="X12" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y12" s="3">
         <v>1000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>100</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>200</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>400</v>
       </c>
       <c r="AC12" s="3">
         <v>200</v>
       </c>
       <c r="AD12" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE12" s="3">
         <v>200</v>
       </c>
-      <c r="AE12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF12" s="3" t="s">
-        <v>3</v>
+      <c r="AF12" s="3">
+        <v>200</v>
       </c>
       <c r="AG12" s="3" t="s">
         <v>3</v>
@@ -1238,8 +1265,14 @@
       <c r="AI12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1339,35 +1372,41 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1440,8 +1479,14 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1541,8 +1586,14 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1575,98 +1626,100 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2100</v>
+        <v>3500</v>
       </c>
       <c r="E17" s="3">
-        <v>1600</v>
+        <v>2400</v>
       </c>
       <c r="F17" s="3">
         <v>2100</v>
       </c>
       <c r="G17" s="3">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="H17" s="3">
         <v>2100</v>
       </c>
       <c r="I17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K17" s="3">
         <v>1700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>2200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3400</v>
-      </c>
-      <c r="L17" s="3">
-        <v>2700</v>
-      </c>
-      <c r="M17" s="3">
-        <v>2300</v>
       </c>
       <c r="N17" s="3">
         <v>2700</v>
       </c>
       <c r="O17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="P17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Q17" s="3">
         <v>3400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>3300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>4300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>2500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>3900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>500</v>
       </c>
-      <c r="AE17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1676,98 +1729,104 @@
       <c r="AI17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-2100</v>
+        <v>-3500</v>
       </c>
       <c r="E18" s="3">
-        <v>-1600</v>
+        <v>-2400</v>
       </c>
       <c r="F18" s="3">
         <v>-2100</v>
       </c>
       <c r="G18" s="3">
-        <v>-1700</v>
+        <v>-1600</v>
       </c>
       <c r="H18" s="3">
         <v>-2100</v>
       </c>
       <c r="I18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="K18" s="3">
         <v>-1700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-2200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3400</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-2300</v>
       </c>
       <c r="N18" s="3">
         <v>-2700</v>
       </c>
       <c r="O18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="Q18" s="3">
         <v>-3400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-3200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-4300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-2200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-2500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-1800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-3900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-500</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1777,8 +1836,14 @@
       <c r="AI18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1814,8 +1879,10 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1828,35 +1895,35 @@
       <c r="F20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
       </c>
       <c r="Q20" s="3">
         <v>-100</v>
@@ -1865,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -1900,11 +1967,11 @@
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
       </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
@@ -1915,98 +1982,104 @@
       <c r="AI20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-2100</v>
+        <v>-3500</v>
       </c>
       <c r="E21" s="3">
-        <v>-1600</v>
+        <v>-2400</v>
       </c>
       <c r="F21" s="3">
         <v>-2100</v>
       </c>
       <c r="G21" s="3">
-        <v>-1700</v>
+        <v>-1600</v>
       </c>
       <c r="H21" s="3">
         <v>-2100</v>
       </c>
       <c r="I21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-1700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-2200</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-3500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-3300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-4300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-2100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-2500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-1800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-3900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-500</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2016,8 +2089,14 @@
       <c r="AI21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2042,11 +2121,11 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2087,20 +2166,20 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD22" s="3" t="s">
-        <v>3</v>
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>0</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>3</v>
@@ -2117,98 +2196,104 @@
       <c r="AI22" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK22" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-2000</v>
       </c>
-      <c r="G23" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J23" s="3">
         <v>-2100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-2200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3500</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-2700</v>
       </c>
       <c r="N23" s="3">
         <v>-2600</v>
       </c>
       <c r="O23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-3500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-3300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-4300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-2100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-1800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-3900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-500</v>
       </c>
-      <c r="AE23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2218,8 +2303,14 @@
       <c r="AI23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2244,11 +2335,11 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2319,8 +2410,14 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2420,98 +2517,104 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-2100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-2000</v>
       </c>
-      <c r="G26" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J26" s="3">
         <v>-2100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-2200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3500</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-2700</v>
       </c>
       <c r="N26" s="3">
         <v>-2600</v>
       </c>
       <c r="O26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-3500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-3300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-4300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-2100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-2500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-3900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-500</v>
       </c>
-      <c r="AE26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2521,98 +2624,104 @@
       <c r="AI26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-2100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2000</v>
       </c>
-      <c r="G27" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J27" s="3">
         <v>-2100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-2200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3500</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="M27" s="3">
-        <v>-2700</v>
       </c>
       <c r="N27" s="3">
         <v>-2600</v>
       </c>
       <c r="O27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-3500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-3300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-4300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-2100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-2500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-3900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-500</v>
       </c>
-      <c r="AE27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2622,8 +2731,14 @@
       <c r="AI27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2723,8 +2838,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2824,8 +2945,14 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2925,8 +3052,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3026,8 +3159,14 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3040,35 +3179,35 @@
       <c r="F32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
       </c>
       <c r="Q32" s="3">
         <v>100</v>
@@ -3077,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T32" s="3">
         <v>0</v>
@@ -3112,11 +3251,11 @@
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
       </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
@@ -3127,98 +3266,104 @@
       <c r="AI32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-2100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2000</v>
       </c>
-      <c r="G33" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J33" s="3">
         <v>-2100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-2200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3500</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="M33" s="3">
-        <v>-2700</v>
       </c>
       <c r="N33" s="3">
         <v>-2600</v>
       </c>
       <c r="O33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-3500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-3300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-4300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-2100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-2500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-3900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-500</v>
       </c>
-      <c r="AE33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3228,8 +3373,14 @@
       <c r="AI33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3329,98 +3480,104 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-2100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2000</v>
       </c>
-      <c r="G35" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J35" s="3">
         <v>-2100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-2200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3500</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="M35" s="3">
-        <v>-2700</v>
       </c>
       <c r="N35" s="3">
         <v>-2600</v>
       </c>
       <c r="O35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-3500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-3300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-4300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-2100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-2500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-3900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-500</v>
       </c>
-      <c r="AE35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3430,103 +3587,109 @@
       <c r="AI35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3536,8 +3699,14 @@
       <c r="AI38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3573,8 +3742,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3610,92 +3781,94 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F41" s="3">
         <v>8000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>9700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>7600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>9300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>11800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>11500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>13000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>6400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>8900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>11300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>6400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>8500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>12400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>15900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>19300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>2600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>4100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>4900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>4300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>3200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>4100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>5200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>700</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3711,8 +3884,14 @@
       <c r="AI41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3735,56 +3914,56 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>1900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>2000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>1600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>1100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>2100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>1300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>2000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>800</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3797,11 +3976,11 @@
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="3">
-        <v>0</v>
+      <c r="AE42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG42" s="3">
         <v>0</v>
@@ -3812,16 +3991,22 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
+      <c r="E43" s="3">
+        <v>0</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
@@ -3832,20 +4017,20 @@
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
+      <c r="I43" s="3">
+        <v>0</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>100</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N43" s="3">
         <v>100</v>
@@ -3856,11 +4041,11 @@
       <c r="P43" s="3">
         <v>100</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
+      <c r="Q43" s="3">
+        <v>100</v>
+      </c>
+      <c r="R43" s="3">
+        <v>100</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
@@ -3874,11 +4059,11 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -3913,8 +4098,14 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3939,11 +4130,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4014,8 +4205,14 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4025,50 +4222,50 @@
       <c r="E45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3">
         <v>600</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>100</v>
-      </c>
-      <c r="L45" s="3">
-        <v>200</v>
-      </c>
-      <c r="M45" s="3">
-        <v>200</v>
       </c>
       <c r="N45" s="3">
         <v>200</v>
       </c>
       <c r="O45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q45" s="3">
         <v>100</v>
       </c>
       <c r="R45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="S45" s="3">
         <v>100</v>
       </c>
       <c r="T45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U45" s="3">
         <v>100</v>
@@ -4089,16 +4286,16 @@
         <v>100</v>
       </c>
       <c r="AA45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC45" s="3">
         <v>200</v>
       </c>
-      <c r="AB45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD45" s="3" t="s">
-        <v>3</v>
+      <c r="AD45" s="3">
+        <v>0</v>
       </c>
       <c r="AE45" s="3" t="s">
         <v>3</v>
@@ -4115,92 +4312,98 @@
       <c r="AI45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F46" s="3">
         <v>8200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>10000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>8400</v>
       </c>
-      <c r="G46" s="3">
-        <v>9400</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J46" s="3">
         <v>12100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>11900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>13400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>6700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>9500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>11900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>8500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>10600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>14800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>17600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>20500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>4800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>5500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>7000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>4900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>2600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>4100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>4200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>5300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>800</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4216,8 +4419,14 @@
       <c r="AI46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4246,10 +4455,10 @@
         <v>0</v>
       </c>
       <c r="L47" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="M47" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="N47" s="3">
         <v>400</v>
@@ -4261,29 +4470,29 @@
         <v>400</v>
       </c>
       <c r="Q47" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="R47" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="S47" s="3">
         <v>500</v>
       </c>
       <c r="T47" s="3">
+        <v>500</v>
+      </c>
+      <c r="U47" s="3">
+        <v>500</v>
+      </c>
+      <c r="V47" s="3">
         <v>400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>300</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4296,11 +4505,11 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD47" s="3">
-        <v>0</v>
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE47" s="3">
         <v>0</v>
@@ -4317,8 +4526,14 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4332,14 +4547,14 @@
         <v>0</v>
       </c>
       <c r="G48" s="3">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3">
         <v>100</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4349,11 +4564,11 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
-      </c>
-      <c r="N48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O48" s="3">
         <v>0</v>
@@ -4397,11 +4612,11 @@
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD48" s="3" t="s">
-        <v>3</v>
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="3">
+        <v>0</v>
       </c>
       <c r="AE48" s="3" t="s">
         <v>3</v>
@@ -4418,8 +4633,14 @@
       <c r="AI48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4519,8 +4740,14 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4620,8 +4847,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4721,8 +4954,14 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4747,11 +4986,11 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -4775,16 +5014,16 @@
         <v>0</v>
       </c>
       <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
         <v>100</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V52" s="3">
-        <v>200</v>
-      </c>
-      <c r="W52" s="3">
-        <v>200</v>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X52" s="3">
         <v>200</v>
@@ -4795,11 +5034,11 @@
       <c r="Z52" s="3">
         <v>200</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
+      <c r="AA52" s="3">
+        <v>200</v>
+      </c>
+      <c r="AB52" s="3">
+        <v>200</v>
       </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
@@ -4807,11 +5046,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>0</v>
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG52" s="3">
         <v>0</v>
@@ -4822,8 +5061,14 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4923,92 +5168,98 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F54" s="3">
         <v>8300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>10000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>8500</v>
       </c>
-      <c r="G54" s="3">
-        <v>9500</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J54" s="3">
         <v>12100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>11900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>13500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>6800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>9900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>12300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>8900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>11000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>15200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>18000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>21000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>5200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>6000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>7400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>5300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>4300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>4400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>5500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>800</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5024,8 +5275,14 @@
       <c r="AI54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5061,8 +5318,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5098,8 +5357,10 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5107,82 +5368,82 @@
         <v>500</v>
       </c>
       <c r="E57" s="3">
+        <v>400</v>
+      </c>
+      <c r="F57" s="3">
+        <v>500</v>
+      </c>
+      <c r="G57" s="3">
         <v>300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
       </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
         <v>700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>800</v>
-      </c>
-      <c r="K57" s="3">
-        <v>700</v>
-      </c>
-      <c r="L57" s="3">
-        <v>900</v>
       </c>
       <c r="M57" s="3">
         <v>700</v>
       </c>
       <c r="N57" s="3">
+        <v>900</v>
+      </c>
+      <c r="O57" s="3">
         <v>700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q57" s="3">
         <v>400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>100</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3">
         <v>200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>400</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="3">
         <v>200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>100</v>
       </c>
-      <c r="AB57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD57" s="3" t="s">
-        <v>3</v>
+      <c r="AD57" s="3">
+        <v>0</v>
       </c>
       <c r="AE57" s="3" t="s">
         <v>3</v>
@@ -5199,8 +5460,14 @@
       <c r="AI57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5300,8 +5567,14 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5326,45 +5599,45 @@
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>700</v>
-      </c>
-      <c r="L59" s="3">
-        <v>100</v>
-      </c>
-      <c r="M59" s="3">
-        <v>100</v>
       </c>
       <c r="N59" s="3">
         <v>100</v>
       </c>
       <c r="O59" s="3">
+        <v>100</v>
+      </c>
+      <c r="P59" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q59" s="3">
         <v>500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>400</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
-      </c>
-      <c r="W59" s="3">
-        <v>0</v>
-      </c>
       <c r="X59" s="3">
         <v>0</v>
       </c>
@@ -5375,22 +5648,22 @@
         <v>0</v>
       </c>
       <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="3">
         <v>200</v>
       </c>
-      <c r="AB59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AE59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF59" s="3">
-        <v>0</v>
+      <c r="AD59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG59" s="3">
         <v>0</v>
@@ -5401,8 +5674,14 @@
       <c r="AI59" s="3">
         <v>0</v>
       </c>
+      <c r="AJ59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5410,82 +5689,82 @@
         <v>800</v>
       </c>
       <c r="E60" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F60" s="3">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="G60" s="3">
         <v>700</v>
       </c>
       <c r="H60" s="3">
+        <v>600</v>
+      </c>
+      <c r="I60" s="3">
+        <v>700</v>
+      </c>
+      <c r="J60" s="3">
         <v>1600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>400</v>
       </c>
-      <c r="X60" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="3">
         <v>200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>300</v>
       </c>
-      <c r="AB60" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD60" s="3" t="s">
-        <v>3</v>
+      <c r="AD60" s="3">
+        <v>0</v>
       </c>
       <c r="AE60" s="3" t="s">
         <v>3</v>
@@ -5502,8 +5781,14 @@
       <c r="AI60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5603,8 +5888,14 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5623,11 +5914,11 @@
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I62" s="3">
-        <v>300</v>
-      </c>
-      <c r="J62" s="3">
-        <v>300</v>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>300</v>
@@ -5639,10 +5930,10 @@
         <v>300</v>
       </c>
       <c r="N62" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O62" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P62" s="3">
         <v>200</v>
@@ -5651,17 +5942,17 @@
         <v>200</v>
       </c>
       <c r="R62" s="3">
+        <v>200</v>
+      </c>
+      <c r="S62" s="3">
+        <v>200</v>
+      </c>
+      <c r="T62" s="3">
         <v>300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>300</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5674,11 +5965,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
@@ -5704,8 +5995,14 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5805,8 +6102,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5906,8 +6209,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6007,8 +6316,14 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -6016,82 +6331,82 @@
         <v>800</v>
       </c>
       <c r="E66" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="F66" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="G66" s="3">
         <v>700</v>
       </c>
       <c r="H66" s="3">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="I66" s="3">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="J66" s="3">
         <v>1600</v>
       </c>
       <c r="K66" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L66" s="3">
         <v>1600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N66" s="3">
         <v>1300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1000</v>
-      </c>
-      <c r="S66" s="3">
-        <v>600</v>
-      </c>
-      <c r="T66" s="3">
-        <v>600</v>
       </c>
       <c r="U66" s="3">
         <v>600</v>
       </c>
       <c r="V66" s="3">
+        <v>600</v>
+      </c>
+      <c r="W66" s="3">
+        <v>600</v>
+      </c>
+      <c r="X66" s="3">
         <v>500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>400</v>
       </c>
-      <c r="X66" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="3">
         <v>200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>300</v>
       </c>
-      <c r="AB66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD66" s="3" t="s">
-        <v>3</v>
+      <c r="AD66" s="3">
+        <v>0</v>
       </c>
       <c r="AE66" s="3" t="s">
         <v>3</v>
@@ -6108,8 +6423,14 @@
       <c r="AI66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6145,8 +6466,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6246,8 +6569,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6347,8 +6676,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6448,8 +6783,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6549,92 +6890,98 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-63900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-60400</v>
+      </c>
+      <c r="F72" s="3">
         <v>-58700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-56600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-55000</v>
       </c>
-      <c r="G72" s="3">
-        <v>-52900</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
+        <v>-52200</v>
+      </c>
+      <c r="J72" s="3">
         <v>-51200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-49200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-47300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-45100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-41600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-39000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-36300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-33700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-30200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-27000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-23700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-19400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-18700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-16500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-14000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-12200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-6600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6650,8 +6997,14 @@
       <c r="AI72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6751,8 +7104,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6852,8 +7211,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6953,92 +7318,98 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F76" s="3">
         <v>7500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>9300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>7800</v>
       </c>
-      <c r="G76" s="3">
-        <v>8800</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
+        <v>9500</v>
+      </c>
+      <c r="J76" s="3">
         <v>10500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>10000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>11900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>5100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>8600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>11200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>7900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>9900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>13300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>16600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>19900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>4600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>5400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>6800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>4800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>2400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>4300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>4200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>5400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>700</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7054,8 +7425,14 @@
       <c r="AI76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7155,103 +7532,109 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
@@ -7261,98 +7644,104 @@
       <c r="AI80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AJ80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-2100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2000</v>
       </c>
-      <c r="G81" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J81" s="3">
         <v>-2100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-2200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3500</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="M81" s="3">
-        <v>-2700</v>
       </c>
       <c r="N81" s="3">
         <v>-2600</v>
       </c>
       <c r="O81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="P81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-3500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-3300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-4300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-2100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-2500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-3900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-500</v>
       </c>
-      <c r="AE81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
@@ -7362,8 +7751,14 @@
       <c r="AI81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7399,8 +7794,10 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7425,11 +7822,11 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -7485,11 +7882,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-      <c r="AE83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>0</v>
       </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
@@ -7500,8 +7897,14 @@
       <c r="AI83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7601,8 +8004,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7702,8 +8111,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7803,8 +8218,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7904,8 +8325,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8005,98 +8432,104 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-3100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-2200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-2100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-3900</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-2800</v>
       </c>
       <c r="R89" s="3">
         <v>-2700</v>
       </c>
       <c r="S89" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="T89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="U89" s="3">
         <v>-700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-1500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-2400</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="W89" s="3">
-        <v>-1500</v>
       </c>
       <c r="X89" s="3">
         <v>-1600</v>
       </c>
       <c r="Y89" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-400</v>
       </c>
-      <c r="AE89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
@@ -8106,8 +8539,14 @@
       <c r="AI89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8143,8 +8582,10 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8169,30 +8610,30 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-100</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
@@ -8244,8 +8685,14 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8345,8 +8792,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8446,8 +8899,14 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8472,54 +8931,54 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>1200</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>1000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-1700</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-900</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
@@ -8532,11 +8991,11 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF94" s="3" t="s">
-        <v>3</v>
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
+        <v>0</v>
       </c>
       <c r="AG94" s="3" t="s">
         <v>3</v>
@@ -8547,8 +9006,14 @@
       <c r="AI94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8584,8 +9049,10 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8610,11 +9077,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8685,8 +9152,14 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8786,8 +9259,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8887,8 +9366,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8988,98 +9473,104 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="E100" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>3700</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>2400</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>8900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>6000</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>18400</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>4500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>4200</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>1600</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>5900</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3">
         <v>1200</v>
       </c>
-      <c r="AE100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
@@ -9089,20 +9580,26 @@
       <c r="AI100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
@@ -9145,11 +9642,11 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>3</v>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>3</v>
@@ -9163,11 +9660,11 @@
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>0</v>
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC101" s="3">
         <v>0</v>
@@ -9190,98 +9687,104 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>2100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-2500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>6600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-2500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-2400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>4900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-2200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-3900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-3500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>16700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>2700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>5100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>800</v>
       </c>
-      <c r="AE102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
@@ -9289,6 +9792,12 @@
         <v>3</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HOTH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HOTH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="92">
   <si>
     <t>HOTH</t>
   </si>
@@ -656,142 +656,143 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="37" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="38" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
@@ -804,8 +805,11 @@
       <c r="AK7" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AL7" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -836,8 +840,8 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N8" s="3">
         <v>0</v>
@@ -911,8 +915,11 @@
       <c r="AK8" s="3">
         <v>0</v>
       </c>
+      <c r="AL8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1018,8 +1025,11 @@
       <c r="AK9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1135,11 @@
       <c r="AK10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1164,100 +1177,101 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="3">
         <v>2000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>600</v>
       </c>
-      <c r="H12" s="3">
-        <v>500</v>
-      </c>
       <c r="I12" s="3">
+        <v>600</v>
+      </c>
+      <c r="J12" s="3">
         <v>1200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>900</v>
-      </c>
-      <c r="M12" s="3">
-        <v>1500</v>
       </c>
       <c r="N12" s="3">
         <v>1500</v>
       </c>
       <c r="O12" s="3">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="P12" s="3">
         <v>1000</v>
       </c>
       <c r="Q12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R12" s="3">
         <v>2000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>1300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>1000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>400</v>
-      </c>
-      <c r="AE12" s="3">
-        <v>200</v>
       </c>
       <c r="AF12" s="3">
         <v>200</v>
       </c>
-      <c r="AG12" s="3" t="s">
-        <v>3</v>
+      <c r="AG12" s="3">
+        <v>200</v>
       </c>
       <c r="AH12" s="3" t="s">
         <v>3</v>
@@ -1271,8 +1285,11 @@
       <c r="AK12" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1378,38 +1395,41 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1485,8 +1505,11 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1592,8 +1615,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1628,101 +1654,102 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E17" s="3">
         <v>3500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2100</v>
       </c>
-      <c r="G17" s="3">
-        <v>1600</v>
-      </c>
       <c r="H17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="J17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K17" s="3">
         <v>2100</v>
       </c>
-      <c r="I17" s="3">
-        <v>2000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2100</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>800</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>600</v>
       </c>
       <c r="AD17" s="3">
         <v>600</v>
       </c>
       <c r="AE17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF17" s="3">
         <v>800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>500</v>
       </c>
-      <c r="AG17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1735,101 +1762,104 @@
       <c r="AK17" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL17" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2100</v>
       </c>
-      <c r="G18" s="3">
-        <v>-1600</v>
-      </c>
       <c r="H18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K18" s="3">
         <v>-2100</v>
       </c>
-      <c r="I18" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-4300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-600</v>
       </c>
       <c r="AD18" s="3">
         <v>-600</v>
       </c>
       <c r="AE18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-500</v>
       </c>
-      <c r="AG18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1842,8 +1872,11 @@
       <c r="AK18" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL18" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1881,8 +1914,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1901,42 +1935,42 @@
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
+      <c r="K20" s="3">
+        <v>0</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1973,8 +2007,8 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-      <c r="AG20" s="3" t="s">
-        <v>3</v>
+      <c r="AG20" s="3">
+        <v>0</v>
       </c>
       <c r="AH20" s="3" t="s">
         <v>3</v>
@@ -1988,41 +2022,44 @@
       <c r="AK20" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL20" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-3500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2100</v>
       </c>
-      <c r="G21" s="3">
-        <v>-1600</v>
-      </c>
       <c r="H21" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K21" s="3">
         <v>-2100</v>
       </c>
-      <c r="I21" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2200</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2032,57 +2069,57 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>-3500</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-3300</v>
       </c>
       <c r="S21" s="3">
         <v>-3300</v>
       </c>
       <c r="T21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="U21" s="3">
         <v>-4300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>-600</v>
       </c>
       <c r="AD21" s="3">
         <v>-600</v>
       </c>
       <c r="AE21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-500</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,8 +2132,11 @@
       <c r="AK21" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2127,8 +2167,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2172,17 +2212,17 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>3</v>
+      <c r="AE22" s="3">
+        <v>0</v>
       </c>
       <c r="AF22" s="3" t="s">
         <v>3</v>
@@ -2202,101 +2242,104 @@
       <c r="AK22" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL22" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2100</v>
       </c>
-      <c r="G23" s="3">
-        <v>-1600</v>
-      </c>
       <c r="H23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J23" s="3">
         <v>-2000</v>
       </c>
-      <c r="I23" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3500</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-3300</v>
       </c>
       <c r="S23" s="3">
         <v>-3300</v>
       </c>
       <c r="T23" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="U23" s="3">
         <v>-4300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC23" s="3">
-        <v>-600</v>
       </c>
       <c r="AD23" s="3">
         <v>-600</v>
       </c>
       <c r="AE23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-500</v>
       </c>
-      <c r="AG23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
@@ -2309,8 +2352,11 @@
       <c r="AK23" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL23" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2341,8 +2387,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -2416,8 +2462,11 @@
       <c r="AK24" s="3">
         <v>0</v>
       </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2523,101 +2572,104 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2100</v>
       </c>
-      <c r="G26" s="3">
-        <v>-1600</v>
-      </c>
       <c r="H26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J26" s="3">
         <v>-2000</v>
       </c>
-      <c r="I26" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3500</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-3300</v>
       </c>
       <c r="S26" s="3">
         <v>-3300</v>
       </c>
       <c r="T26" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="U26" s="3">
         <v>-4300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>-600</v>
       </c>
       <c r="AD26" s="3">
         <v>-600</v>
       </c>
       <c r="AE26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-500</v>
       </c>
-      <c r="AG26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2630,101 +2682,104 @@
       <c r="AK26" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL26" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2100</v>
       </c>
-      <c r="G27" s="3">
-        <v>-1600</v>
-      </c>
       <c r="H27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J27" s="3">
         <v>-2000</v>
       </c>
-      <c r="I27" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3500</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-3300</v>
       </c>
       <c r="S27" s="3">
         <v>-3300</v>
       </c>
       <c r="T27" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="U27" s="3">
         <v>-4300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>-600</v>
       </c>
       <c r="AD27" s="3">
         <v>-600</v>
       </c>
       <c r="AE27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-500</v>
       </c>
-      <c r="AG27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2737,8 +2792,11 @@
       <c r="AK27" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL27" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2844,8 +2902,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2951,8 +3012,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3058,8 +3122,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3165,8 +3232,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3185,42 +3255,42 @@
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
+      <c r="K32" s="3">
+        <v>0</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -3257,8 +3327,8 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-      <c r="AG32" s="3" t="s">
-        <v>3</v>
+      <c r="AG32" s="3">
+        <v>0</v>
       </c>
       <c r="AH32" s="3" t="s">
         <v>3</v>
@@ -3272,101 +3342,104 @@
       <c r="AK32" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL32" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2100</v>
       </c>
-      <c r="G33" s="3">
-        <v>-1600</v>
-      </c>
       <c r="H33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J33" s="3">
         <v>-2000</v>
       </c>
-      <c r="I33" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3500</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-3300</v>
       </c>
       <c r="S33" s="3">
         <v>-3300</v>
       </c>
       <c r="T33" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="U33" s="3">
         <v>-4300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>-600</v>
       </c>
       <c r="AD33" s="3">
         <v>-600</v>
       </c>
       <c r="AE33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-500</v>
       </c>
-      <c r="AG33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
@@ -3379,8 +3452,11 @@
       <c r="AK33" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL33" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3486,101 +3562,104 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2100</v>
       </c>
-      <c r="G35" s="3">
-        <v>-1600</v>
-      </c>
       <c r="H35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J35" s="3">
         <v>-2000</v>
       </c>
-      <c r="I35" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3500</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-3300</v>
       </c>
       <c r="S35" s="3">
         <v>-3300</v>
       </c>
       <c r="T35" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="U35" s="3">
         <v>-4300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>-600</v>
       </c>
       <c r="AD35" s="3">
         <v>-600</v>
       </c>
       <c r="AE35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-500</v>
       </c>
-      <c r="AG35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3593,106 +3672,109 @@
       <c r="AK35" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL35" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3705,8 +3787,11 @@
       <c r="AK38" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AL38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3744,8 +3829,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3783,95 +3869,96 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E41" s="3">
         <v>11300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>9300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>12400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>15900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>19300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>700</v>
       </c>
-      <c r="AE41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3890,8 +3977,11 @@
       <c r="AK41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3920,52 +4010,52 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M42" s="3">
         <v>200</v>
       </c>
       <c r="N42" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O42" s="3">
         <v>300</v>
       </c>
       <c r="P42" s="3">
-        <v>1900</v>
+        <v>300</v>
       </c>
       <c r="Q42" s="3">
         <v>1900</v>
       </c>
       <c r="R42" s="3">
+        <v>1900</v>
+      </c>
+      <c r="S42" s="3">
         <v>2000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>500</v>
-      </c>
-      <c r="Y42" s="3">
-        <v>800</v>
       </c>
       <c r="Z42" s="3">
         <v>800</v>
       </c>
-      <c r="AA42" s="3" t="s">
-        <v>3</v>
+      <c r="AA42" s="3">
+        <v>800</v>
       </c>
       <c r="AB42" s="3" t="s">
         <v>3</v>
@@ -3982,8 +4072,8 @@
       <c r="AF42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG42" s="3">
-        <v>0</v>
+      <c r="AG42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH42" s="3">
         <v>0</v>
@@ -3997,19 +4087,22 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>0</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
+      <c r="F43" s="3">
+        <v>0</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>3</v>
@@ -4017,11 +4110,11 @@
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3">
+        <v>0</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
@@ -4029,11 +4122,11 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O43" s="3">
         <v>100</v>
@@ -4047,8 +4140,8 @@
       <c r="R43" s="3">
         <v>100</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
+      <c r="S43" s="3">
+        <v>100</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
@@ -4065,8 +4158,8 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -4104,8 +4197,11 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4136,8 +4232,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4211,8 +4307,11 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4228,12 +4327,12 @@
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>600</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4243,11 +4342,11 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>100</v>
-      </c>
-      <c r="N45" s="3">
-        <v>200</v>
       </c>
       <c r="O45" s="3">
         <v>200</v>
@@ -4256,19 +4355,19 @@
         <v>200</v>
       </c>
       <c r="Q45" s="3">
+        <v>200</v>
+      </c>
+      <c r="R45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
-      </c>
-      <c r="U45" s="3">
-        <v>100</v>
       </c>
       <c r="V45" s="3">
         <v>100</v>
@@ -4292,13 +4391,13 @@
         <v>100</v>
       </c>
       <c r="AC45" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD45" s="3">
         <v>200</v>
       </c>
-      <c r="AD45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE45" s="3" t="s">
-        <v>3</v>
+      <c r="AE45" s="3">
+        <v>0</v>
       </c>
       <c r="AF45" s="3" t="s">
         <v>3</v>
@@ -4318,95 +4417,98 @@
       <c r="AK45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E46" s="3">
         <v>12300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>10200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>12100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>17600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>20500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>7000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>800</v>
       </c>
-      <c r="AE46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4425,8 +4527,11 @@
       <c r="AK46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4461,7 +4566,7 @@
         <v>0</v>
       </c>
       <c r="N47" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="O47" s="3">
         <v>400</v>
@@ -4476,7 +4581,7 @@
         <v>400</v>
       </c>
       <c r="S47" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="T47" s="3">
         <v>500</v>
@@ -4485,17 +4590,17 @@
         <v>500</v>
       </c>
       <c r="V47" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="W47" s="3">
         <v>400</v>
       </c>
       <c r="X47" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y47" s="3">
         <v>300</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4511,8 +4616,8 @@
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE47" s="3">
-        <v>0</v>
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF47" s="3">
         <v>0</v>
@@ -4532,8 +4637,11 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4553,11 +4661,11 @@
         <v>0</v>
       </c>
       <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
         <v>100</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4570,8 +4678,8 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -4618,8 +4726,8 @@
       <c r="AD48" s="3">
         <v>0</v>
       </c>
-      <c r="AE48" s="3" t="s">
-        <v>3</v>
+      <c r="AE48" s="3">
+        <v>0</v>
       </c>
       <c r="AF48" s="3" t="s">
         <v>3</v>
@@ -4639,8 +4747,11 @@
       <c r="AK48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4746,8 +4857,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4853,8 +4967,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4960,8 +5077,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4992,8 +5112,8 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -5020,13 +5140,13 @@
         <v>0</v>
       </c>
       <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3">
         <v>100</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X52" s="3">
-        <v>200</v>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y52" s="3">
         <v>200</v>
@@ -5040,8 +5160,8 @@
       <c r="AB52" s="3">
         <v>200</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
+      <c r="AC52" s="3">
+        <v>200</v>
       </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
@@ -5052,8 +5172,8 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG52" s="3">
-        <v>0</v>
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH52" s="3">
         <v>0</v>
@@ -5067,8 +5187,11 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5174,95 +5297,98 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E54" s="3">
         <v>12400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>8300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>12100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>18000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>21000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>800</v>
       </c>
-      <c r="AE54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
@@ -5281,8 +5407,11 @@
       <c r="AK54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5320,8 +5449,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5359,94 +5489,95 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>100</v>
+      </c>
+      <c r="E57" s="3">
         <v>500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>400</v>
       </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
       <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3">
         <v>700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>900</v>
-      </c>
-      <c r="O57" s="3">
-        <v>700</v>
       </c>
       <c r="P57" s="3">
         <v>700</v>
       </c>
       <c r="Q57" s="3">
+        <v>700</v>
+      </c>
+      <c r="R57" s="3">
         <v>400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>100</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
       <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3">
         <v>200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>400</v>
       </c>
-      <c r="Z57" s="3">
-        <v>0</v>
-      </c>
       <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="3">
         <v>200</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>100</v>
       </c>
       <c r="AC57" s="3">
         <v>100</v>
       </c>
       <c r="AD57" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="AE57" s="3">
+        <v>0</v>
       </c>
       <c r="AF57" s="3" t="s">
         <v>3</v>
@@ -5466,8 +5597,11 @@
       <c r="AK57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5573,8 +5707,11 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5605,11 +5742,11 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
         <v>700</v>
-      </c>
-      <c r="N59" s="3">
-        <v>100</v>
       </c>
       <c r="O59" s="3">
         <v>100</v>
@@ -5618,29 +5755,29 @@
         <v>100</v>
       </c>
       <c r="Q59" s="3">
+        <v>100</v>
+      </c>
+      <c r="R59" s="3">
         <v>500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>400</v>
-      </c>
-      <c r="T59" s="3">
-        <v>200</v>
       </c>
       <c r="U59" s="3">
         <v>200</v>
       </c>
       <c r="V59" s="3">
+        <v>200</v>
+      </c>
+      <c r="W59" s="3">
         <v>500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>400</v>
       </c>
-      <c r="X59" s="3">
-        <v>0</v>
-      </c>
       <c r="Y59" s="3">
         <v>0</v>
       </c>
@@ -5654,19 +5791,19 @@
         <v>0</v>
       </c>
       <c r="AC59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="3">
         <v>200</v>
       </c>
-      <c r="AD59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE59" s="3" t="s">
-        <v>3</v>
+      <c r="AE59" s="3">
+        <v>0</v>
       </c>
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AG59" s="3">
-        <v>0</v>
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AH59" s="3">
         <v>0</v>
@@ -5680,13 +5817,16 @@
       <c r="AK59" s="3">
         <v>0</v>
       </c>
+      <c r="AL59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E60" s="3">
         <v>800</v>
@@ -5695,79 +5835,79 @@
         <v>800</v>
       </c>
       <c r="G60" s="3">
+        <v>800</v>
+      </c>
+      <c r="H60" s="3">
         <v>700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1000</v>
-      </c>
-      <c r="O60" s="3">
-        <v>800</v>
       </c>
       <c r="P60" s="3">
         <v>800</v>
       </c>
       <c r="Q60" s="3">
+        <v>800</v>
+      </c>
+      <c r="R60" s="3">
         <v>900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>300</v>
-      </c>
-      <c r="V60" s="3">
-        <v>600</v>
       </c>
       <c r="W60" s="3">
         <v>600</v>
       </c>
       <c r="X60" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y60" s="3">
         <v>500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>400</v>
       </c>
-      <c r="Z60" s="3">
-        <v>0</v>
-      </c>
       <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="3">
         <v>200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>300</v>
       </c>
-      <c r="AD60" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE60" s="3" t="s">
-        <v>3</v>
+      <c r="AE60" s="3">
+        <v>0</v>
       </c>
       <c r="AF60" s="3" t="s">
         <v>3</v>
@@ -5787,8 +5927,11 @@
       <c r="AK60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5894,8 +6037,11 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5920,8 +6066,8 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>300</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L62" s="3">
         <v>300</v>
@@ -5936,7 +6082,7 @@
         <v>300</v>
       </c>
       <c r="P62" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q62" s="3">
         <v>200</v>
@@ -5948,13 +6094,13 @@
         <v>200</v>
       </c>
       <c r="T62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U62" s="3">
         <v>300</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
+      <c r="V62" s="3">
+        <v>300</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
@@ -5971,8 +6117,8 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -6001,8 +6147,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6108,8 +6257,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6215,8 +6367,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6322,13 +6477,16 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E66" s="3">
         <v>800</v>
@@ -6337,7 +6495,7 @@
         <v>800</v>
       </c>
       <c r="G66" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="H66" s="3">
         <v>700</v>
@@ -6346,40 +6504,40 @@
         <v>700</v>
       </c>
       <c r="J66" s="3">
+        <v>700</v>
+      </c>
+      <c r="K66" s="3">
         <v>1600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2000</v>
-      </c>
-      <c r="L66" s="3">
-        <v>1600</v>
       </c>
       <c r="M66" s="3">
         <v>1600</v>
       </c>
       <c r="N66" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O66" s="3">
         <v>1300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1000</v>
-      </c>
-      <c r="P66" s="3">
-        <v>1100</v>
       </c>
       <c r="Q66" s="3">
         <v>1100</v>
       </c>
       <c r="R66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S66" s="3">
         <v>1800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1000</v>
-      </c>
-      <c r="U66" s="3">
-        <v>600</v>
       </c>
       <c r="V66" s="3">
         <v>600</v>
@@ -6388,28 +6546,28 @@
         <v>600</v>
       </c>
       <c r="X66" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y66" s="3">
         <v>500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>400</v>
       </c>
-      <c r="Z66" s="3">
-        <v>0</v>
-      </c>
       <c r="AA66" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB66" s="3">
         <v>200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>300</v>
       </c>
-      <c r="AD66" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE66" s="3" t="s">
-        <v>3</v>
+      <c r="AE66" s="3">
+        <v>0</v>
       </c>
       <c r="AF66" s="3" t="s">
         <v>3</v>
@@ -6429,8 +6587,11 @@
       <c r="AK66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6468,8 +6629,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6575,8 +6737,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6682,8 +6847,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6789,8 +6957,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6896,95 +7067,98 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-66100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-63900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-60400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-58700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-56600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-55000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-52200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-51200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-49200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-47300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-45100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-41600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-39000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-36300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-33700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-30200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-27000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-23700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-19400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-18700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-16500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-14000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
@@ -7003,8 +7177,11 @@
       <c r="AK72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7110,8 +7287,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7217,8 +7397,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7324,95 +7507,98 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E76" s="3">
         <v>11500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>10000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>19900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>700</v>
       </c>
-      <c r="AE76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
@@ -7431,8 +7617,11 @@
       <c r="AK76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7538,106 +7727,109 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
@@ -7650,101 +7842,104 @@
       <c r="AK80" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="AL80" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2100</v>
       </c>
-      <c r="G81" s="3">
-        <v>-1600</v>
-      </c>
       <c r="H81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="J81" s="3">
         <v>-2000</v>
       </c>
-      <c r="I81" s="3">
-        <v>-2000</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3500</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-3300</v>
       </c>
       <c r="S81" s="3">
         <v>-3300</v>
       </c>
       <c r="T81" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="U81" s="3">
         <v>-4300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-800</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>-600</v>
       </c>
       <c r="AD81" s="3">
         <v>-600</v>
       </c>
       <c r="AE81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-500</v>
       </c>
-      <c r="AG81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
@@ -7757,8 +7952,11 @@
       <c r="AK81" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL81" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7796,8 +7994,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7828,8 +8027,8 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -7888,8 +8087,8 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>3</v>
+      <c r="AG83" s="3">
+        <v>0</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>3</v>
@@ -7903,8 +8102,11 @@
       <c r="AK83" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL83" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8010,8 +8212,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8117,8 +8322,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8224,8 +8432,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8331,8 +8542,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8438,101 +8652,104 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2000</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-1600</v>
       </c>
       <c r="G89" s="3">
         <v>-1600</v>
       </c>
       <c r="H89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I89" s="3">
         <v>-1700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-3100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-400</v>
       </c>
-      <c r="AG89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
@@ -8545,8 +8762,11 @@
       <c r="AK89" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL89" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8584,8 +8804,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8616,8 +8837,8 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>-100</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
@@ -8626,17 +8847,17 @@
         <v>-100</v>
       </c>
       <c r="P91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
@@ -8691,8 +8912,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8798,8 +9022,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8905,8 +9132,11 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8937,51 +9167,51 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>1200</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
         <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1700</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-900</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
         <v>0</v>
       </c>
@@ -8997,8 +9227,8 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>3</v>
+      <c r="AG94" s="3">
+        <v>0</v>
       </c>
       <c r="AH94" s="3" t="s">
         <v>3</v>
@@ -9012,8 +9242,11 @@
       <c r="AK94" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL94" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9051,8 +9284,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9083,8 +9317,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9158,8 +9392,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9265,8 +9502,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9372,8 +9612,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9479,89 +9722,92 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>7100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1100</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>3700</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>2400</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>8900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>6000</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
         <v>0</v>
       </c>
       <c r="R100" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S100" s="3">
         <v>-100</v>
       </c>
       <c r="T100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U100" s="3">
         <v>18400</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>4500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>4200</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>1600</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>5900</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
         <v>0</v>
       </c>
@@ -9569,11 +9815,11 @@
         <v>0</v>
       </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>1200</v>
       </c>
-      <c r="AG100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
@@ -9586,8 +9832,11 @@
       <c r="AK100" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AL100" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9595,14 +9844,14 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
@@ -9648,8 +9897,8 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>3</v>
+      <c r="W101" s="3">
+        <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>3</v>
@@ -9666,8 +9915,8 @@
       <c r="AB101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
+      <c r="AC101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD101" s="3">
         <v>0</v>
@@ -9693,101 +9942,104 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E102" s="3">
         <v>4300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>16700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>5100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>800</v>
       </c>
-      <c r="AG102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AH102" s="3" t="s">
         <v>3</v>
       </c>
@@ -9798,6 +10050,9 @@
         <v>3</v>
       </c>
       <c r="AK102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
